--- a/Documents/Product Catalog/Home/Dining Table Set.xlsx
+++ b/Documents/Product Catalog/Home/Dining Table Set.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CB6348-2FBB-421B-89FD-7AF442465F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dining Set " sheetId="5" r:id="rId1"/>
@@ -17,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Dining Set '!$A$1:$Q$14</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -538,7 +552,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="9">
     <font>
       <sz val="10"/>
@@ -782,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -850,11 +864,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1086,7 +1097,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -1095,7 +1106,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1134,7 +1145,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000048010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1184,7 +1195,7 @@
         <xdr:cNvPr id="71" name="image229.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-0000F8000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1234,7 +1245,7 @@
         <xdr:cNvPr id="72" name="image230.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-0000F9000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1284,7 +1295,7 @@
         <xdr:cNvPr id="73" name="image224.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-0000F3000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1334,7 +1345,7 @@
         <xdr:cNvPr id="74" name="image239.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1379,7 +1390,7 @@
         <xdr:cNvPr id="10" name="image240.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1429,7 +1440,7 @@
         <xdr:cNvPr id="11" name="image266.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00001D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1476,7 +1487,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1514,7 +1531,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1555,7 +1578,7 @@
         <xdr:cNvPr id="14" name="image242.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000005010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1600,7 +1623,7 @@
         <xdr:cNvPr id="15" name="image240.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1650,7 +1673,7 @@
         <xdr:cNvPr id="16" name="image266.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00001D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1934,7 +1957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AT80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
@@ -1959,89 +1982,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="30" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="30" t="s">
+      <c r="L3" s="29"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="Q3" s="29" t="s">
         <v>20</v>
       </c>
       <c r="S3" s="4"/>
@@ -2074,22 +2097,22 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="24" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="32"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="31"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2099,10 +2122,10 @@
       <c r="M4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
